--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,121 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -813,41 +821,47 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>2932900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5174200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2173500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4572300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2586000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4077200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1620100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3984500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2407800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4229100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -893,38 +907,44 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>2780100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>2415700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>2122300</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>2061000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>2172800</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -970,38 +990,44 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>2394100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>2156600</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1954800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1923500</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2056300</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1217,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1230,38 +1270,44 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>124500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>-34900</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>28200</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>38500</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1800</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1304,11 +1350,11 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1337,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,8 +1415,10 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1410,38 +1464,44 @@
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>4358400</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>3608300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>3427400</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>3341200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>3553900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1487,38 +1547,44 @@
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>815800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>964100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>649700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>643300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>675200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1593,38 +1661,44 @@
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-38800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-33300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>13400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>5300</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1670,38 +1744,44 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>1087600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>1547400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>926400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>1244900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>1000600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1747,8 +1827,8 @@
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R22" s="3">
-        <v>37100</v>
+      <c r="R22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>5</v>
@@ -1760,25 +1840,31 @@
         <v>5</v>
       </c>
       <c r="V22" s="3">
+        <v>37100</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>36000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>34900</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>34500</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1824,38 +1910,44 @@
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>739900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>893700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>612200</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>621900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>646000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1901,38 +1993,44 @@
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>162800</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>152500</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>157300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>145900</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>168000</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,8 +2106,14 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2055,38 +2159,44 @@
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>577200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>741200</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>454900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>476000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>478100</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2132,38 +2242,44 @@
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>487800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>642700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>385800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>425800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>418800</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2286,38 +2408,44 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>-1258000</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>-87000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>44700</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2517,38 +2657,44 @@
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>38800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>33300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>1600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2594,38 +2740,44 @@
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>-770100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>555700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>430400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>425800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>418800</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,8 +2853,14 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2748,120 +2906,132 @@
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>-770100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>555700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>430400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>425800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>418800</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,56 +3090,58 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1506900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1505800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1487300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1368800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1602300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1726300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1538600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1548900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1984500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1898100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1647100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1638800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1172800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2995,61 +3169,67 @@
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>74400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>75100</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>102800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>94600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>8200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>8800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>331600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>317100</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3072,56 +3252,62 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2814800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2841600</v>
+      </c>
+      <c r="F43" s="3">
         <v>1742700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1741400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2600900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2393700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1056200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1137900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1764900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1776700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1176600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1125300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1798100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1789000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1118700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3149,56 +3335,62 @@
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1207500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1219000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1117800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1117000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1262400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1161900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>826400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>890300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>936900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>943100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>861800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>824200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>982100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>977100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>821600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3226,8 +3418,14 @@
       <c r="AA44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3261,21 +3459,21 @@
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>1478200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1470800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1669300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3303,56 +3501,62 @@
       <c r="AA45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5497400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5549800</v>
+      </c>
+      <c r="F46" s="3">
         <v>4598300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4594900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5453400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5019000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3657500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3940500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4240400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4268600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4478300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4283200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5905500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5875600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4920800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3380,56 +3584,62 @@
       <c r="AA46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>679900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>679400</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>631100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>679900</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>806300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>771200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>793500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3457,56 +3667,62 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5197300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5246900</v>
+      </c>
+      <c r="F48" s="3">
         <v>5153400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5149700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4874100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4485800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3755600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4046100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3602900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3626900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3619200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3461500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3457900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3440400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3402200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3534,56 +3750,62 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12839700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>12962200</v>
+      </c>
+      <c r="F49" s="3">
         <v>13084800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>13075400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12758300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11741900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7382000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>7953200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7070000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>7117200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>7281400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6964200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>7186600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>7150200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7072300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3611,8 +3833,14 @@
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,56 +3999,62 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1482400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1496600</v>
+      </c>
+      <c r="F52" s="3">
         <v>205300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>205200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1256500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1156400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>27300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>29500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1217500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1225600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>33200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>31800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1186800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1180800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>42000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3842,8 +4082,14 @@
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,56 +4165,62 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25016700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25255400</v>
+      </c>
+      <c r="F54" s="3">
         <v>24203400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>24185900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>24342300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>22403100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>15824600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>17049000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16130800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>16238300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>16584200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>15861800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17736800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>17647100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>16572000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3996,8 +4248,14 @@
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,56 +4314,58 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4738800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4784000</v>
+      </c>
+      <c r="F57" s="3">
         <v>4225400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4222300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4531800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4170800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3233900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3484100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3707200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3731900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3286100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3143000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3672400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3653800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3149000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4131,56 +4393,62 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1371200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1384300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1441800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1440700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1144400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1053200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1492100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1607500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>902800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>908900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1236500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1182600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1996400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1986300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>830600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4208,56 +4476,62 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2246800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2268200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1964800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1963400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2143700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1973000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1663100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1791800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2535700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2552600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2481500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2373400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3231600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3215200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3024300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4285,56 +4559,62 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8356800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8436500</v>
+      </c>
+      <c r="F60" s="3">
         <v>7632000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7626400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7819900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7197000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6389000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6883300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7145800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7193400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7004100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6699000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8900400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8855300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7003900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4362,56 +4642,62 @@
       <c r="AA60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7814600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7889200</v>
+      </c>
+      <c r="F61" s="3">
         <v>9660900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9653900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>10518200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9680300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3802600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4096800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4424300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4453800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4562100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4363300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3103800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3088100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3285200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4439,56 +4725,62 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2019100</v>
+      </c>
+      <c r="F62" s="3">
         <v>520200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>519800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1632400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1502400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>497000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>535400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1112300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1119700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>278700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>266500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1230500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1224300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>374900</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4516,8 +4808,14 @@
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,56 +5057,62 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18171400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18344800</v>
+      </c>
+      <c r="F66" s="3">
         <v>19380800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>19366800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>19970500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18379600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11575000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12470600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12682400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12766900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12765700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>12209600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13234700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13167700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>11583200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4824,8 +5140,14 @@
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,56 +5503,62 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4320400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4361700</v>
+      </c>
+      <c r="F72" s="3">
         <v>4456100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4452900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4033400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3712100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3551300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3826100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3086700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3107300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3456200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3305700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10183900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>10132400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10169000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5238,8 +5586,14 @@
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,56 +5835,62 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6407400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6468500</v>
+      </c>
+      <c r="F76" s="3">
         <v>4371100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4367900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3939100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3625300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3855200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4153500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3112100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3132900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3445500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3295400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4146100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4125100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4583600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5546,8 +5918,14 @@
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,90 +6001,102 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5752,38 +6142,44 @@
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>-770100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>555700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>430400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>425800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>418800</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,85 +6207,93 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>217800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>200500</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
         <v>149900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>150900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>136100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>130200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>143400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>142700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>149700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>158800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>169300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>310600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>671000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>303500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>588200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>320100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>539400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>544600</v>
+      </c>
+      <c r="F89" s="3">
         <v>559700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>559300</v>
       </c>
-      <c r="F89" s="3">
-        <v>418000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>384700</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="H89" s="3">
+        <v>437100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>402300</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>422500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>425300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>183800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>175800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>596100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>593100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>1223200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>1929200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>950500</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>1465600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>749900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,55 +6819,57 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-259900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-189300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-189100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-198000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-182300</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-156700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-157700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-155300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-148600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-131300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-130700</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -6439,25 +6881,31 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-235900</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-589500</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-363900</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-328400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-331500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-164500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-164400</v>
       </c>
-      <c r="F94" s="3">
-        <v>-2519300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-2318600</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="H94" s="3">
+        <v>-2501600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-2302300</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>8800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-326600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-312400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-170300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-169500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-158500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-591700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-179600</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-787400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-289100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,85 +7182,93 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>293700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>296500</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>280900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>258600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>258700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>260400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>270800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>269400</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="R96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-494700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-463700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-453200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-414800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-453700</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,235 +7510,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-248200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-250500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-337800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-337600</v>
       </c>
-      <c r="F100" s="3">
-        <v>1937000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>1782700</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="H100" s="3">
+        <v>1900200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1748800</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>-624700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-628900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>123800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>118400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-22000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-21900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-328100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-713100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-242700</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-73200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="D101" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-15900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-15200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-74400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-74000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>27500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>29200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>22900</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>57100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>66600</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>22600</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-58700</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="F102" s="3">
         <v>51500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>51400</v>
       </c>
-      <c r="F102" s="3">
-        <v>-205800</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-189400</v>
-      </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>-207300</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-190800</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-192000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-193300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-34800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-33300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>329400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>327800</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>793600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>56200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>59400</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>376700</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>370800</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
